--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-138</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>R$ 1.464.149,71</t>
-  </si>
-  <si>
-    <t>R$ 9.960,20
-R$ 10.177,47</t>
-  </si>
-  <si>
-    <t>6.4%
-8.8%</t>
-  </si>
-  <si>
-    <t>105.0</t>
-  </si>
-  <si>
-    <t>(1.4%)</t>
-  </si>
-  <si>
-    <t>(695.9%)</t>
-  </si>
-  <si>
-    <t>(741.7%)</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>31.5</t>
-  </si>
-  <si>
-    <t>57.1%</t>
-  </si>
-  <si>
-    <t>19.8%</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>8.5</t>
-  </si>
-  <si>
-    <t>14.5</t>
+171</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.778.269,04</t>
+  </si>
+  <si>
+    <t>R$ 9.770,71
+R$ 10.002,75</t>
+  </si>
+  <si>
+    <t>6.1%
+8.4%</t>
+  </si>
+  <si>
+    <t>102.5</t>
+  </si>
+  <si>
+    <t>(2.3%)</t>
+  </si>
+  <si>
+    <t>(568.6%)</t>
+  </si>
+  <si>
+    <t>(613.3%)</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>31.6</t>
+  </si>
+  <si>
+    <t>55.9%</t>
+  </si>
+  <si>
+    <t>20.4%</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>16.4</t>
   </si>
   <si>
     <t>23.0</t>
   </si>
   <si>
-    <t>57.2%</t>
-  </si>
-  <si>
-    <t>-R$ 38.108,13</t>
+    <t>56.8%</t>
+  </si>
+  <si>
+    <t>-R$ 48.678,43</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1411,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -1884,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.2258337500000005</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>10.591457999999999</v>
+      </c>
       <c r="AD4" s="8">
         <v>15.828125</v>
       </c>
@@ -2064,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2100,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>17017.27</v>
+      </c>
+      <c r="P6" s="5">
+        <v>17017.27</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.53833713610049427</v>
+      </c>
+      <c r="R6" s="7">
+        <v>163</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.32520325203252032</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.26026825101793644</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.020368419846426598</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.021672600834328887</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.00058284907038555532</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.717901481481483</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.97037037037037033</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.9955484472049694</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.1491159090909089</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.06677</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>15.946542962962964</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.97037037037037033</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -2370,7 +2408,9 @@
       <c r="AB8" s="8">
         <v>3.7613402061855674</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>13.767697</v>
+      </c>
       <c r="AD8" s="8">
         <v>20.706873195876291</v>
       </c>
@@ -2499,7 +2539,9 @@
       <c r="AB9" s="8">
         <v>4.1375703389830507</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>18.424423999999998</v>
+      </c>
       <c r="AD9" s="8">
         <v>24.171273983739837</v>
       </c>
@@ -2626,7 +2668,9 @@
       <c r="AB10" s="8">
         <v>3.3272151898734181</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>12.153465000000001</v>
+      </c>
       <c r="AD10" s="8">
         <v>19.01458375</v>
       </c>
@@ -2677,7 +2721,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>44</v>
@@ -2713,25 +2757,61 @@
       <c t="s" r="N11" s="4">
         <v>52</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="6"/>
+      <c r="O11" s="5">
+        <v>14544.200000000001</v>
+      </c>
+      <c r="P11" s="5">
+        <v>14544.200000000001</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0.24459497736158742</v>
+      </c>
+      <c r="R11" s="7">
+        <v>144</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0.16129032258064524</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0.31752722734835881</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0.037133668403899839</v>
+      </c>
+      <c r="V11" s="6">
+        <v>0.023724955652425019</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.0041618308329093388</v>
+      </c>
+      <c r="X11" s="8">
+        <v>26.7488203539823</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>0.22123893805309736</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0.061946902654867256</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>6.5719909722222223</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>6.5875378378378375</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>13.289275999999999</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>19.043510619469028</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0.68141592920353977</v>
+      </c>
       <c r="AF11" s="9"/>
-      <c r="AG11" s="5"/>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
       <c r="AH11" s="10">
         <v>3</v>
       </c>
@@ -2903,7 +2983,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2939,25 +3019,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>14474.139999999999</v>
+      </c>
+      <c r="P13" s="5">
+        <v>14474.139999999999</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.039701974781971239</v>
+      </c>
+      <c r="R13" s="7">
+        <v>151</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.067901234567901203</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.35418641798407369</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.011898033320114356</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.021976158859870087</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.017612514456817469</v>
+      </c>
+      <c r="X13" s="8">
+        <v>37.415749541284406</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.59633027522935778</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.38532110091743121</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>12.627527096774193</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>6.6518348623853205</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>20.484860999999999</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>27.430887155963301</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.19266055045871561</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-70.900000000000006</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3207,7 +3323,9 @@
       <c r="AB15" s="8">
         <v>3.7059055118110233</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>9.8103660000000001</v>
+      </c>
       <c r="AD15" s="8">
         <v>16.764041732283467</v>
       </c>
@@ -3258,7 +3376,7 @@
         <v>19520</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>44</v>
@@ -3294,25 +3412,61 @@
       <c t="s" r="N16" s="4">
         <v>52</v>
       </c>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="6"/>
+      <c r="O16" s="5">
+        <v>3226.8499999999999</v>
+      </c>
+      <c r="P16" s="5">
+        <v>3226.8499999999999</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>-0.063285590706153583</v>
+      </c>
+      <c r="R16" s="7">
+        <v>35</v>
+      </c>
+      <c r="S16" s="6">
+        <v>-0.10256410256410253</v>
+      </c>
+      <c r="T16" s="6">
+        <v>-0.0085665587182546452</v>
+      </c>
+      <c r="U16" s="6">
+        <v>-0.32629127477261111</v>
+      </c>
+      <c r="V16" s="6">
+        <v>0.032192695662953033</v>
+      </c>
+      <c r="W16" s="6">
+        <v>-0.019318840355145112</v>
+      </c>
+      <c r="X16" s="8">
+        <v>66.91666923076923</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z16" s="6">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="AA16" s="8">
+        <v>7.5761914285714287</v>
+      </c>
+      <c r="AB16" s="8">
+        <v>10.9</v>
+      </c>
+      <c r="AC16" s="8">
+        <v>17.041025000000001</v>
+      </c>
+      <c r="AD16" s="8">
+        <v>23.410609090909091</v>
+      </c>
+      <c r="AE16" s="6">
+        <v>0.53846153846153844</v>
+      </c>
       <c r="AF16" s="9"/>
-      <c r="AG16" s="5"/>
+      <c r="AG16" s="5">
+        <v>-155.80000000000001</v>
+      </c>
       <c r="AH16" s="10">
         <v>3</v>
       </c>
@@ -3353,7 +3507,7 @@
         <v>19521</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>44</v>
@@ -3389,10 +3543,16 @@
       <c t="s" r="N17" s="4">
         <v>52</v>
       </c>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="7"/>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
@@ -3407,7 +3567,9 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="6"/>
       <c r="AF17" s="9"/>
-      <c r="AG17" s="5"/>
+      <c r="AG17" s="5">
+        <v>0</v>
+      </c>
       <c r="AH17" s="10">
         <v>5</v>
       </c>
@@ -3657,7 +3819,9 @@
       <c r="AB19" s="8">
         <v>8.437341772151898</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>11.626507</v>
+      </c>
       <c r="AD19" s="8">
         <v>18.432499999999997</v>
       </c>
@@ -3786,7 +3950,9 @@
       <c r="AB20" s="8">
         <v>4.2461290322580645</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>19.36092</v>
+      </c>
       <c r="AD20" s="8">
         <v>26.122823566878981</v>
       </c>
@@ -3915,7 +4081,9 @@
       <c r="AB21" s="8">
         <v>5.1618055555555555</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>9.5474530000000009</v>
+      </c>
       <c r="AD21" s="8">
         <v>15.503472222222221</v>
       </c>
@@ -4175,7 +4343,9 @@
       <c r="AB23" s="8">
         <v>9.4671485549132957</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>16.225197000000001</v>
+      </c>
       <c r="AD23" s="8">
         <v>22.910795454545454</v>
       </c>
@@ -4399,7 +4569,9 @@
       <c r="AB25" s="8">
         <v>8.9331764150943389</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>25.282388999999998</v>
+      </c>
       <c r="AD25" s="8">
         <v>32.191509433962267</v>
       </c>
@@ -4528,7 +4700,9 @@
       <c r="AB26" s="8">
         <v>19.114242727272725</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>25.767896</v>
+      </c>
       <c r="AD26" s="8">
         <v>30.69971779661017</v>
       </c>
@@ -4657,7 +4831,9 @@
       <c r="AB27" s="8">
         <v>4.9595244897959176</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>8.3811269999999993</v>
+      </c>
       <c r="AD27" s="8">
         <v>15.89551346153846</v>
       </c>
@@ -4708,7 +4884,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4744,25 +4920,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>6707.0500000000002</v>
+      </c>
+      <c r="P28" s="5">
+        <v>6707.0500000000002</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.035375716475580798</v>
+      </c>
+      <c r="R28" s="7">
+        <v>76</v>
+      </c>
+      <c r="S28" s="6">
+        <v>-0.025641025641025661</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00026390141716551988</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.28244310091620012</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.077032600025346468</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.067846743352144384</v>
+      </c>
+      <c r="X28" s="8">
+        <v>23.492197872340423</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.57446808510638303</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>1.9050232876712327</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>7.6624106382978727</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>9.4886520000000001</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>16.395036170212766</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.80851063829787229</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-972.13999999999999</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5008,7 +5220,9 @@
       <c r="AB30" s="8">
         <v>12.820941025641027</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>16.16094</v>
+      </c>
       <c r="AD30" s="8">
         <v>22.6304175</v>
       </c>
@@ -5139,7 +5353,9 @@
       <c r="AB31" s="8">
         <v>4.5456013888888886</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>8.1570160000000005</v>
+      </c>
       <c r="AD31" s="8">
         <v>16.095601388888888</v>
       </c>
@@ -5268,7 +5484,9 @@
       <c r="AB32" s="8">
         <v>9.7577653409090903</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>17.131587</v>
+      </c>
       <c r="AD32" s="8">
         <v>23.072632386363637</v>
       </c>
@@ -5319,7 +5537,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>44</v>
@@ -5353,25 +5571,61 @@
       <c t="s" r="N33" s="4">
         <v>52</v>
       </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="8"/>
-      <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="6"/>
+      <c r="O33" s="5">
+        <v>12450.16</v>
+      </c>
+      <c r="P33" s="5">
+        <v>12450.16</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>0.46626169313951449</v>
+      </c>
+      <c r="R33" s="7">
+        <v>117</v>
+      </c>
+      <c r="S33" s="6">
+        <v>0.32954545454545459</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.31765333136280982</v>
+      </c>
+      <c r="U33" s="6">
+        <v>0.015349585868775984</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.013733197003090725</v>
+      </c>
+      <c r="W33" s="6">
+        <v>-0.003671398600499913</v>
+      </c>
+      <c r="X33" s="8">
+        <v>24.340351315789473</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0.039473684210526314</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>2.3084033613445376</v>
+      </c>
+      <c r="AB33" s="8">
+        <v>6.5875560000000002</v>
+      </c>
+      <c r="AC33" s="8">
+        <v>8.7540019999999998</v>
+      </c>
+      <c r="AD33" s="8">
+        <v>15.594078947368422</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>0.76315789473684215</v>
+      </c>
       <c r="AF33" s="9"/>
-      <c r="AG33" s="5"/>
+      <c r="AG33" s="5">
+        <v>0</v>
+      </c>
       <c r="AH33" s="10">
         <v>5</v>
       </c>
@@ -5815,7 +6069,9 @@
       <c r="AB37" s="8">
         <v>9.2477427083333339</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>30.145617999999999</v>
+      </c>
       <c r="AD37" s="8">
         <v>37.148148484848484</v>
       </c>
@@ -5944,7 +6200,9 @@
       <c r="AB38" s="8">
         <v>6.3991556962025316</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>9.2310490000000005</v>
+      </c>
       <c r="AD38" s="8">
         <v>15.945472839506174</v>
       </c>
@@ -5995,7 +6253,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6031,25 +6289,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>13968.049999999999</v>
+      </c>
+      <c r="P39" s="5">
+        <v>13968.049999999999</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>-0.077966596211808237</v>
+      </c>
+      <c r="R39" s="7">
+        <v>157</v>
+      </c>
+      <c r="S39" s="6">
+        <v>-0.076470588235294068</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.23139113906379202</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.066353356409806663</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.053173241791087518</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.032014955559294248</v>
+      </c>
+      <c r="X39" s="8">
+        <v>38.01052631578947</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.35964912280701755</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>3.9988398734177215</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>18.412649107142858</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>22.540717999999998</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>30.088157894736845</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.42982456140350878</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6168,7 +6462,9 @@
       <c r="AB40" s="8">
         <v>6.3398041176470583</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>10.32122</v>
+      </c>
       <c r="AD40" s="8">
         <v>17.05067456647399</v>
       </c>
@@ -6297,7 +6593,9 @@
       <c r="AB41" s="8">
         <v>10.301716176470588</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>13.405286</v>
+      </c>
       <c r="AD41" s="8">
         <v>19.127053623188406</v>
       </c>
@@ -6443,7 +6741,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6479,25 +6777,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>9222.3500000000004</v>
+      </c>
+      <c r="P43" s="5">
+        <v>9222.3500000000004</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>-0.21003784342177167</v>
+      </c>
+      <c r="R43" s="7">
+        <v>94</v>
+      </c>
+      <c r="S43" s="6">
+        <v>-0.3037037037037037</v>
+      </c>
+      <c r="T43" s="6">
+        <v>-0.00015046056590782174</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.33227730459156285</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.020092763774959745</v>
+      </c>
+      <c r="W43" s="6">
+        <v>0.0043180425813377282</v>
+      </c>
+      <c r="X43" s="8">
+        <v>49.627949230769225</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.35384615384615387</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>7.2464915789473681</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>21.547090476190476</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>29.024108999999999</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>35.029487692307697</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.12307692307692308</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>-95.299999999999997</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -6747,7 +7081,9 @@
       <c r="AB45" s="8">
         <v>7.6926409090909091</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>24.746276000000002</v>
+      </c>
       <c r="AD45" s="8">
         <v>30.711645512820514</v>
       </c>
@@ -6872,7 +7208,9 @@
       <c r="AB46" s="8">
         <v>9.4295454545454547</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>17.772656000000001</v>
+      </c>
       <c r="AD46" s="8">
         <v>23.374073611111111</v>
       </c>
@@ -7130,7 +7468,9 @@
       <c r="AB48" s="8">
         <v>7.6846774193548386</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>14.895258999999999</v>
+      </c>
       <c r="AD48" s="8">
         <v>21.69126984126984</v>
       </c>
@@ -7310,7 +7650,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7346,25 +7686,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>13364.43</v>
+      </c>
+      <c r="P50" s="5">
+        <v>13364.43</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.059657479788633672</v>
+      </c>
+      <c r="R50" s="7">
+        <v>143</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.14371257485029942</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.19357113621755662</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.07974691775107505</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.04429758695282926</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.023707109094813619</v>
+      </c>
+      <c r="X50" s="8">
+        <v>25.089936792452832</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.96226415094339623</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>3.1914916083916087</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>8.3577780952380945</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>11.661789000000001</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>19.409591509433966</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.78301886792452835</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7707,7 +8083,9 @@
       <c r="AB53" s="8">
         <v>4.6921564705882357</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>8.5399989999999999</v>
+      </c>
       <c r="AD53" s="8">
         <v>15.446862352941178</v>
       </c>
@@ -7836,7 +8214,9 @@
       <c r="AB54" s="8">
         <v>7.3223044117647058</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>11.451468999999999</v>
+      </c>
       <c r="AD54" s="8">
         <v>18.374264705882354</v>
       </c>
@@ -7887,7 +8267,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -7923,25 +8303,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>7906.2399999999998</v>
+      </c>
+      <c r="P55" s="5">
+        <v>7906.2399999999998</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.15935778841042003</v>
+      </c>
+      <c r="R55" s="7">
+        <v>94</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.1454545454545455</v>
+      </c>
+      <c r="T55" s="6">
+        <v>-8.3478366454850855E-05</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.33409939490832558</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.065736747176913427</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.035054653033553249</v>
+      </c>
+      <c r="X55" s="8">
+        <v>40.438815789473686</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.039473684210526314</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.46052631578947367</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.3388367924528302</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>14.281140789473685</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>17.550042000000001</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>24.55811447368421</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.21052631578947367</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8058,7 +8474,9 @@
       <c r="AB56" s="8">
         <v>6.8682075630252095</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>13.525539999999999</v>
+      </c>
       <c r="AD56" s="8">
         <v>21.57950819672131</v>
       </c>
@@ -8187,7 +8605,9 @@
       <c r="AB57" s="8">
         <v>18.904629365079366</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>38.986282000000003</v>
+      </c>
       <c r="AD57" s="8">
         <v>45.528084251968508</v>
       </c>
@@ -8411,7 +8831,9 @@
       <c r="AB59" s="8">
         <v>7.3767681818181812</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>10.679182000000001</v>
+      </c>
       <c r="AD59" s="8">
         <v>17.376368656716416</v>
       </c>
@@ -8540,7 +8962,9 @@
       <c r="AB60" s="8">
         <v>7.7940298507462691</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>11.965043</v>
+      </c>
       <c r="AD60" s="8">
         <v>19.789705882352941</v>
       </c>
@@ -8667,7 +9091,9 @@
       <c r="AB61" s="8">
         <v>15.823164406779661</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>20.292653999999999</v>
+      </c>
       <c r="AD61" s="8">
         <v>27.173728813559322</v>
       </c>
@@ -8716,7 +9142,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8752,25 +9178,61 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="O62" s="5">
+        <v>12816.09</v>
+      </c>
+      <c r="P62" s="5">
+        <v>12816.09</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.33101692960015283</v>
+      </c>
+      <c r="R62" s="7">
+        <v>120</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="T62" s="6">
+        <v>-2.0130944773327904E-06</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.27209748058885358</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.037752192751455402</v>
+      </c>
+      <c r="W62" s="6">
+        <v>0.025676746964167697</v>
+      </c>
+      <c r="X62" s="8">
+        <v>25.957201234567901</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.4567901234567901</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0.024691358024691357</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>3.8439262711864406</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>7.38396582278481</v>
+      </c>
+      <c r="AC62" s="8">
+        <v>11.420385</v>
+      </c>
+      <c r="AD62" s="8">
+        <v>18.084774074074076</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>0.7407407407407407</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -8889,7 +9351,9 @@
       <c r="AB63" s="8">
         <v>14.480889333333334</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>21.148420000000002</v>
+      </c>
       <c r="AD63" s="8">
         <v>26.890131578947368</v>
       </c>
@@ -9240,7 +9704,9 @@
       <c r="AB66" s="8">
         <v>3.8705882352941177</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>7.6058079999999997</v>
+      </c>
       <c r="AD66" s="8">
         <v>14.289423076923075</v>
       </c>
@@ -9367,7 +9833,9 @@
       <c r="AB67" s="8">
         <v>13.303332727272728</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>14.936363</v>
+      </c>
       <c r="AD67" s="8">
         <v>21.867576363636363</v>
       </c>
@@ -9549,7 +10017,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>44</v>
@@ -9583,25 +10051,61 @@
       <c t="s" r="N69" s="4">
         <v>52</v>
       </c>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
-      <c r="X69" s="8"/>
-      <c r="Y69" s="6"/>
-      <c r="Z69" s="6"/>
-      <c r="AA69" s="8"/>
-      <c r="AB69" s="8"/>
-      <c r="AC69" s="8"/>
-      <c r="AD69" s="8"/>
-      <c r="AE69" s="6"/>
+      <c r="O69" s="5">
+        <v>9237.0599999999995</v>
+      </c>
+      <c r="P69" s="5">
+        <v>9237.0599999999995</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0.23764108775578019</v>
+      </c>
+      <c r="R69" s="7">
+        <v>107</v>
+      </c>
+      <c r="S69" s="6">
+        <v>0.22988505747126431</v>
+      </c>
+      <c r="T69" s="6">
+        <v>0</v>
+      </c>
+      <c r="U69" s="6">
+        <v>-0.33150915984090179</v>
+      </c>
+      <c r="V69" s="6">
+        <v>0.019290553487798064</v>
+      </c>
+      <c r="W69" s="6">
+        <v>-0.0043760677098557332</v>
+      </c>
+      <c r="X69" s="8">
+        <v>25.920481927710846</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>0.66265060240963858</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="AA69" s="8">
+        <v>3.3833330275229359</v>
+      </c>
+      <c r="AB69" s="8">
+        <v>5.1746913580246909</v>
+      </c>
+      <c r="AC69" s="8">
+        <v>8.3377429999999997</v>
+      </c>
+      <c r="AD69" s="8">
+        <v>16.04196746987952</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>0.77108433734939763</v>
+      </c>
       <c r="AF69" s="9"/>
-      <c r="AG69" s="5"/>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
       <c r="AH69" s="10">
         <v>2</v>
       </c>
@@ -9773,7 +10277,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9807,25 +10311,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>16315.23</v>
+      </c>
+      <c r="P71" s="5">
+        <v>16315.23</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.10973691137670061</v>
+      </c>
+      <c r="R71" s="7">
+        <v>182</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.03703703703703709</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.2547213125404913</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.046409593980593598</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.031517821078832477</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.01167746332721022</v>
+      </c>
+      <c r="X71" s="8">
+        <v>22.186731067961166</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.98058252427184467</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.0097087378640776691</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>3.3058988764044948</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>4.3514999999999997</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>7.9452499999999997</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>15.562459223300969</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.92233009708737868</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-384.5</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10071,7 +10611,9 @@
       <c r="AB73" s="8">
         <v>17.939086904761904</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>21.201101999999999</v>
+      </c>
       <c r="AD73" s="8">
         <v>28.841176470588234</v>
       </c>
@@ -10213,7 +10755,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10249,25 +10791,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>6656.6999999999998</v>
+      </c>
+      <c r="P75" s="5">
+        <v>6656.6999999999998</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.11586807418701883</v>
+      </c>
+      <c r="R75" s="7">
+        <v>72</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.1910112359550562</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.30208211275857405</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.047270494389111725</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.028324169633602236</v>
+      </c>
+      <c r="X75" s="8">
+        <v>30.577778571428571</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>3.7342597222222218</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>13.059348780487806</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>16.797720999999999</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>23.240078571428572</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.52380952380952384</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-690.89999999999998</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10308,7 +10886,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10342,25 +10920,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>5624.9099999999999</v>
+      </c>
+      <c r="P76" s="5">
+        <v>5624.9099999999999</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.46321765369398049</v>
+      </c>
+      <c r="R76" s="7">
+        <v>67</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.46825396825396826</v>
+      </c>
+      <c r="T76" s="6">
+        <v>1.5831093119712139</v>
+      </c>
+      <c r="U76" s="6">
+        <v>1.1932452963691864</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.091124924665461307</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.067604548339440101</v>
+      </c>
+      <c r="X76" s="8">
+        <v>43.394790624999999</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.3125</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.4316176470588236</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>7.0390625</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>10.748151999999999</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>19.718228125</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.34375</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-104.7</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -10479,7 +11093,9 @@
       <c r="AB77" s="8">
         <v>1.9698919354838711</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>9.3830639999999992</v>
+      </c>
       <c r="AD77" s="8">
         <v>16.333870967741937</v>
       </c>
@@ -10604,7 +11220,9 @@
       <c r="AB78" s="8">
         <v>4.5456932584269669</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>7.1586949999999998</v>
+      </c>
       <c r="AD78" s="8">
         <v>15.132771910112361</v>
       </c>
@@ -10991,7 +11609,9 @@
       <c r="AB81" s="8">
         <v>7.4783333333333335</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>15.478332999999999</v>
+      </c>
       <c r="AD81" s="8">
         <v>22.156110000000002</v>
       </c>
@@ -11120,7 +11740,9 @@
       <c r="AB82" s="8">
         <v>9.0182926829268286</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>16.481300000000001</v>
+      </c>
       <c r="AD82" s="8">
         <v>23.371137804878046</v>
       </c>
@@ -11342,7 +11964,9 @@
       <c r="AB84" s="8">
         <v>8.2346500000000002</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>17.380583000000001</v>
+      </c>
       <c r="AD84" s="8">
         <v>23.550812195121953</v>
       </c>
@@ -11471,7 +12095,9 @@
       <c r="AB85" s="8">
         <v>34.812823076923081</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>42.990597000000001</v>
+      </c>
       <c r="AD85" s="8">
         <v>50.015384615384619</v>
       </c>
@@ -11600,7 +12226,9 @@
       <c r="AB86" s="8">
         <v>2.7346660000000003</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>9.8613949999999999</v>
+      </c>
       <c r="AD86" s="8">
         <v>18.037500000000001</v>
       </c>
@@ -11729,7 +12357,9 @@
       <c r="AB87" s="8">
         <v>21.819483098591547</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>49.467604999999999</v>
+      </c>
       <c r="AD87" s="8">
         <v>56.409390140845069</v>
       </c>
@@ -11856,7 +12486,9 @@
       <c r="AB88" s="8">
         <v>6.1914587500000007</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>9.1343440000000005</v>
+      </c>
       <c r="AD88" s="8">
         <v>15.372083749999998</v>
       </c>
@@ -12078,7 +12710,9 @@
       <c r="AB90" s="8">
         <v>17.844117647058823</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>27.119852000000002</v>
+      </c>
       <c r="AD90" s="8">
         <v>34.04509852941176</v>
       </c>
@@ -12207,7 +12841,9 @@
       <c r="AB91" s="8">
         <v>4.7572921875</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>13.90211</v>
+      </c>
       <c r="AD91" s="8">
         <v>19.742793243243241</v>
       </c>
@@ -12594,7 +13230,9 @@
       <c r="AB94" s="8">
         <v>11.746666250000001</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>23.712721999999999</v>
+      </c>
       <c r="AD94" s="8">
         <v>31.479012345679013</v>
       </c>
@@ -12816,7 +13454,9 @@
       <c r="AB96" s="8">
         <v>4.081746428571428</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>6.5068409999999997</v>
+      </c>
       <c r="AD96" s="8">
         <v>13.423214285714286</v>
       </c>
@@ -12945,7 +13585,9 @@
       <c r="AB97" s="8">
         <v>2.1065979166666664</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>12.969995000000001</v>
+      </c>
       <c r="AD97" s="8">
         <v>18.634641176470588</v>
       </c>
@@ -13074,7 +13716,9 @@
       <c r="AB98" s="8">
         <v>16.010465116279072</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>26.344168</v>
+      </c>
       <c r="AD98" s="8">
         <v>32.937879545454543</v>
       </c>
@@ -13463,7 +14107,9 @@
       <c r="AB101" s="8">
         <v>9.25</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>13.819046999999999</v>
+      </c>
       <c r="AD101" s="8">
         <v>20.27523714285714</v>
       </c>
@@ -13592,7 +14238,9 @@
       <c r="AB102" s="8">
         <v>21.258928571428573</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>30.223870000000002</v>
+      </c>
       <c r="AD102" s="8">
         <v>36.417250877192984</v>
       </c>
@@ -13905,7 +14553,7 @@
         <v>19722</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C105" s="4">
         <v>44</v>
@@ -13939,25 +14587,61 @@
       <c t="s" r="N105" s="4">
         <v>52</v>
       </c>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="6"/>
-      <c r="R105" s="7"/>
-      <c r="S105" s="6"/>
-      <c r="T105" s="6"/>
-      <c r="U105" s="6"/>
-      <c r="V105" s="6"/>
-      <c r="W105" s="6"/>
-      <c r="X105" s="8"/>
-      <c r="Y105" s="6"/>
-      <c r="Z105" s="6"/>
-      <c r="AA105" s="8"/>
-      <c r="AB105" s="8"/>
-      <c r="AC105" s="8"/>
-      <c r="AD105" s="8"/>
-      <c r="AE105" s="6"/>
+      <c r="O105" s="5">
+        <v>6414.6199999999999</v>
+      </c>
+      <c r="P105" s="5">
+        <v>6414.6199999999999</v>
+      </c>
+      <c r="Q105" s="6">
+        <v>-0.11219035544938427</v>
+      </c>
+      <c r="R105" s="7">
+        <v>59</v>
+      </c>
+      <c r="S105" s="6">
+        <v>-0.14492753623188404</v>
+      </c>
+      <c r="T105" s="6">
+        <v>0</v>
+      </c>
+      <c r="U105" s="6">
+        <v>-4.2705522696589977</v>
+      </c>
+      <c r="V105" s="6">
+        <v>0.014817089710692139</v>
+      </c>
+      <c r="W105" s="6">
+        <v>-0.0061163404847052521</v>
+      </c>
+      <c r="X105" s="8">
+        <v>31.35408163265306</v>
+      </c>
+      <c r="Y105" s="6">
+        <v>0.38775510204081631</v>
+      </c>
+      <c r="Z105" s="6">
+        <v>0.24489795918367346</v>
+      </c>
+      <c r="AA105" s="8">
+        <v>4.7722222222222221</v>
+      </c>
+      <c r="AB105" s="8">
+        <v>14.38939318181818</v>
+      </c>
+      <c r="AC105" s="8">
+        <v>19.213291999999999</v>
+      </c>
+      <c r="AD105" s="8">
+        <v>23.244218367346939</v>
+      </c>
+      <c r="AE105" s="6">
+        <v>0.59183673469387754</v>
+      </c>
       <c r="AF105" s="9"/>
-      <c r="AG105" s="5"/>
+      <c r="AG105" s="5">
+        <v>-100</v>
+      </c>
       <c r="AH105" s="10">
         <v>2</v>
       </c>
@@ -14429,7 +15113,9 @@
       <c r="AB109" s="8">
         <v>17.791025641025641</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>23.745190999999998</v>
+      </c>
       <c r="AD109" s="8">
         <v>31.43205128205128</v>
       </c>
@@ -14651,7 +15337,9 @@
       <c r="AB111" s="8">
         <v>1.5842105263157895</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>7.7823580000000003</v>
+      </c>
       <c r="AD111" s="8">
         <v>14.41491052631579</v>
       </c>
@@ -14871,7 +15559,9 @@
       <c r="AB113" s="8">
         <v>8.2371276422764232</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>15.22526</v>
+      </c>
       <c r="AD113" s="8">
         <v>25.044892741935481</v>
       </c>
@@ -14922,7 +15612,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>44</v>
@@ -14958,25 +15648,61 @@
       <c t="s" r="N114" s="4">
         <v>52</v>
       </c>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
-      <c r="V114" s="6"/>
-      <c r="W114" s="6"/>
-      <c r="X114" s="8"/>
-      <c r="Y114" s="6"/>
-      <c r="Z114" s="6"/>
-      <c r="AA114" s="8"/>
-      <c r="AB114" s="8"/>
-      <c r="AC114" s="8"/>
-      <c r="AD114" s="8"/>
-      <c r="AE114" s="6"/>
+      <c r="O114" s="5">
+        <v>21524.689999999999</v>
+      </c>
+      <c r="P114" s="5">
+        <v>21524.689999999999</v>
+      </c>
+      <c r="Q114" s="6">
+        <v>0.51601220715539897</v>
+      </c>
+      <c r="R114" s="7">
+        <v>184</v>
+      </c>
+      <c r="S114" s="6">
+        <v>0.26027397260273966</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0.26137818477292823</v>
+      </c>
+      <c r="U114" s="6">
+        <v>-0.0097425607523267468</v>
+      </c>
+      <c r="V114" s="6">
+        <v>0.010041120220546731</v>
+      </c>
+      <c r="W114" s="6">
+        <v>0.0039383610170460066</v>
+      </c>
+      <c r="X114" s="8">
+        <v>34.019697202797204</v>
+      </c>
+      <c r="Y114" s="6">
+        <v>0.34265734265734266</v>
+      </c>
+      <c r="Z114" s="6">
+        <v>0.2937062937062937</v>
+      </c>
+      <c r="AA114" s="8">
+        <v>10.628218518518519</v>
+      </c>
+      <c r="AB114" s="8">
+        <v>6.6335746376811597</v>
+      </c>
+      <c r="AC114" s="8">
+        <v>17.980083</v>
+      </c>
+      <c r="AD114" s="8">
+        <v>25.299650349650349</v>
+      </c>
+      <c r="AE114" s="6">
+        <v>0.43356643356643354</v>
+      </c>
       <c r="AF114" s="9"/>
-      <c r="AG114" s="5"/>
+      <c r="AG114" s="5">
+        <v>-628</v>
+      </c>
       <c r="AH114" s="10">
         <v>2</v>
       </c>
@@ -15241,7 +15967,7 @@
         <v>19745</v>
       </c>
       <c r="B117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C117" s="4">
         <v>44</v>
@@ -15277,25 +16003,61 @@
       <c t="s" r="N117" s="4">
         <v>52</v>
       </c>
-      <c r="O117" s="5"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="6"/>
-      <c r="R117" s="7"/>
-      <c r="S117" s="6"/>
-      <c r="T117" s="6"/>
-      <c r="U117" s="6"/>
-      <c r="V117" s="6"/>
-      <c r="W117" s="6"/>
-      <c r="X117" s="8"/>
-      <c r="Y117" s="6"/>
-      <c r="Z117" s="6"/>
-      <c r="AA117" s="8"/>
-      <c r="AB117" s="8"/>
-      <c r="AC117" s="8"/>
-      <c r="AD117" s="8"/>
-      <c r="AE117" s="6"/>
+      <c r="O117" s="5">
+        <v>7290.3000000000002</v>
+      </c>
+      <c r="P117" s="5">
+        <v>7290.3000000000002</v>
+      </c>
+      <c r="Q117" s="6">
+        <v>0.072508286219938878</v>
+      </c>
+      <c r="R117" s="7">
+        <v>74</v>
+      </c>
+      <c r="S117" s="6">
+        <v>0</v>
+      </c>
+      <c r="T117" s="6">
+        <v>0.25903656913981593</v>
+      </c>
+      <c r="U117" s="6">
+        <v>-0.0078303636338696633</v>
+      </c>
+      <c r="V117" s="6">
+        <v>0.035363359532529524</v>
+      </c>
+      <c r="W117" s="6">
+        <v>0.014878605818690587</v>
+      </c>
+      <c r="X117" s="8">
+        <v>25.49285714285714</v>
+      </c>
+      <c r="Y117" s="6">
+        <v>0.32142857142857145</v>
+      </c>
+      <c r="Z117" s="6">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="AA117" s="8">
+        <v>6.618115942028985</v>
+      </c>
+      <c r="AB117" s="8">
+        <v>13.856861764705883</v>
+      </c>
+      <c r="AC117" s="8">
+        <v>20.658646999999998</v>
+      </c>
+      <c r="AD117" s="8">
+        <v>20.416964285714283</v>
+      </c>
+      <c r="AE117" s="6">
+        <v>0.6964285714285714</v>
+      </c>
       <c r="AF117" s="9"/>
-      <c r="AG117" s="5"/>
+      <c r="AG117" s="5">
+        <v>-115.7</v>
+      </c>
       <c r="AH117" s="10">
         <v>3</v>
       </c>
@@ -15414,7 +16176,9 @@
       <c r="AB118" s="8">
         <v>19.214123728813558</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>28.028639999999999</v>
+      </c>
       <c r="AD118" s="8">
         <v>33.851612903225806</v>
       </c>
@@ -15543,7 +16307,9 @@
       <c r="AB119" s="8">
         <v>4.4104838709677416</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>6.8316470000000002</v>
+      </c>
       <c r="AD119" s="8">
         <v>13.803495161290321</v>
       </c>
@@ -15670,7 +16436,9 @@
       <c r="AB120" s="8">
         <v>13.108332692307691</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>19.339742999999999</v>
+      </c>
       <c r="AD120" s="8">
         <v>27.278525000000002</v>
       </c>
@@ -15797,7 +16565,9 @@
       <c r="AB121" s="8">
         <v>6.219840476190476</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>13.428553000000001</v>
+      </c>
       <c r="AD121" s="8">
         <v>20.836363636363636</v>
       </c>
@@ -15926,7 +16696,9 @@
       <c r="AB122" s="8">
         <v>5.0744796875000002</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>8.5874989999999993</v>
+      </c>
       <c r="AD122" s="8">
         <v>15.5302078125</v>
       </c>
@@ -16186,7 +16958,9 @@
       <c r="AB124" s="8">
         <v>9.3870388888888883</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>18.190370000000001</v>
+      </c>
       <c r="AD124" s="8">
         <v>25.74648947368421</v>
       </c>
@@ -16368,7 +17142,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16404,25 +17178,53 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
+      <c r="O126" s="5">
+        <v>0</v>
+      </c>
+      <c r="P126" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R126" s="7">
+        <v>51</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.52777777777777779</v>
+      </c>
       <c r="T126" s="6"/>
       <c r="U126" s="6"/>
       <c r="V126" s="6"/>
       <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
-      <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="X126" s="8">
+        <v>41.388332500000004</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>6.132025490196078</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>17.3070825</v>
+      </c>
+      <c r="AC126" s="8">
+        <v>23.367796999999999</v>
+      </c>
+      <c r="AD126" s="8">
+        <v>30.3491675</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -16672,7 +17474,9 @@
       <c r="AB128" s="8">
         <v>15.664196296296295</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>29.919751999999999</v>
+      </c>
       <c r="AD128" s="8">
         <v>36.76728518518518</v>
       </c>
@@ -16801,7 +17605,9 @@
       <c r="AB129" s="8">
         <v>6.8404030303030305</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>13.792424</v>
+      </c>
       <c r="AD129" s="8">
         <v>20.714142424242425</v>
       </c>
@@ -16930,7 +17736,9 @@
       <c r="AB130" s="8">
         <v>20.869005263157895</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>24.404281999999998</v>
+      </c>
       <c r="AD130" s="8">
         <v>31.330994736842104</v>
       </c>
@@ -17057,7 +17865,9 @@
       <c r="AB131" s="8">
         <v>10.905950000000001</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>18.342856000000001</v>
+      </c>
       <c r="AD131" s="8">
         <v>25.298807142857139</v>
       </c>
@@ -17239,7 +18049,7 @@
         <v>19775</v>
       </c>
       <c r="B133" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C133" s="4">
         <v>44</v>
@@ -17275,25 +18085,61 @@
       <c t="s" r="N133" s="4">
         <v>52</v>
       </c>
-      <c r="O133" s="5"/>
-      <c r="P133" s="5"/>
-      <c r="Q133" s="6"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="6"/>
-      <c r="T133" s="6"/>
-      <c r="U133" s="6"/>
-      <c r="V133" s="6"/>
-      <c r="W133" s="6"/>
-      <c r="X133" s="8"/>
-      <c r="Y133" s="6"/>
-      <c r="Z133" s="6"/>
-      <c r="AA133" s="8"/>
-      <c r="AB133" s="8"/>
-      <c r="AC133" s="8"/>
-      <c r="AD133" s="8"/>
-      <c r="AE133" s="6"/>
+      <c r="O133" s="5">
+        <v>8037.4799999999996</v>
+      </c>
+      <c r="P133" s="5">
+        <v>8037.4799999999996</v>
+      </c>
+      <c r="Q133" s="6">
+        <v>-0.060999274499656031</v>
+      </c>
+      <c r="R133" s="7">
+        <v>81</v>
+      </c>
+      <c r="S133" s="6">
+        <v>-0.15625</v>
+      </c>
+      <c r="T133" s="6">
+        <v>0.0018612799036513935</v>
+      </c>
+      <c r="U133" s="6">
+        <v>-0.35015950272971136</v>
+      </c>
+      <c r="V133" s="6">
+        <v>0.0030431179922065124</v>
+      </c>
+      <c r="W133" s="6">
+        <v>-0.0086719966954816683</v>
+      </c>
+      <c r="X133" s="8">
+        <v>21.875640384615387</v>
+      </c>
+      <c r="Y133" s="6">
+        <v>0.20754716981132076</v>
+      </c>
+      <c r="Z133" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA133" s="8">
+        <v>4.4739211764705882</v>
+      </c>
+      <c r="AB133" s="8">
+        <v>8.1960794117647051</v>
+      </c>
+      <c r="AC133" s="8">
+        <v>12.140522000000001</v>
+      </c>
+      <c r="AD133" s="8">
+        <v>14.41474423076923</v>
+      </c>
+      <c r="AE133" s="6">
+        <v>0.80769230769230771</v>
+      </c>
       <c r="AF133" s="9"/>
-      <c r="AG133" s="5"/>
+      <c r="AG133" s="5">
+        <v>-142.24000000000001</v>
+      </c>
       <c r="AH133" s="10">
         <v>1</v>
       </c>
@@ -17412,7 +18258,9 @@
       <c r="AB134" s="8">
         <v>59.520137500000004</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>67.913193000000007</v>
+      </c>
       <c r="AD134" s="8">
         <v>75.158333333333331</v>
       </c>
@@ -17594,7 +18442,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -17630,25 +18478,61 @@
       <c t="s" r="N136" s="4">
         <v>52</v>
       </c>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="8"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-      <c r="AA136" s="8"/>
-      <c r="AB136" s="8"/>
-      <c r="AC136" s="8"/>
-      <c r="AD136" s="8"/>
-      <c r="AE136" s="6"/>
+      <c r="O136" s="5">
+        <v>8075.1999999999998</v>
+      </c>
+      <c r="P136" s="5">
+        <v>8075.1999999999998</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>-0.19368624537691603</v>
+      </c>
+      <c r="R136" s="7">
+        <v>82</v>
+      </c>
+      <c r="S136" s="6">
+        <v>-0.14583333333333337</v>
+      </c>
+      <c r="T136" s="6">
+        <v>0.29390473300970876</v>
+      </c>
+      <c r="U136" s="6">
+        <v>-0.0031467332078462451</v>
+      </c>
+      <c r="V136" s="6">
+        <v>0.0085281479096492967</v>
+      </c>
+      <c r="W136" s="6">
+        <v>-0.0048585174361006535</v>
+      </c>
+      <c r="X136" s="8">
+        <v>36.437179487179485</v>
+      </c>
+      <c r="Y136" s="6">
+        <v>0.35897435897435898</v>
+      </c>
+      <c r="Z136" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA136" s="8">
+        <v>9.152880246913579</v>
+      </c>
+      <c r="AB136" s="8">
+        <v>14.828071052631577</v>
+      </c>
+      <c r="AC136" s="8">
+        <v>23.930634000000001</v>
+      </c>
+      <c r="AD136" s="8">
+        <v>30.338033333333332</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>0.48717948717948717</v>
+      </c>
       <c r="AF136" s="9"/>
-      <c r="AG136" s="5"/>
+      <c r="AG136" s="5">
+        <v>-547.89999999999998</v>
+      </c>
       <c r="AH136" s="10">
         <v>2</v>
       </c>
@@ -17765,7 +18649,9 @@
       <c r="AB137" s="8">
         <v>6.4585714285714291</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>14.540051999999999</v>
+      </c>
       <c r="AD137" s="8">
         <v>21.489522857142855</v>
       </c>
@@ -17892,7 +18778,9 @@
       <c r="AB138" s="8">
         <v>7.6967857142857143</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>15.346546</v>
+      </c>
       <c r="AD138" s="8">
         <v>21.642013888888886</v>
       </c>
@@ -18021,7 +18909,9 @@
       <c r="AB139" s="8">
         <v>8.4874207547169807</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>23.911002</v>
+      </c>
       <c r="AD139" s="8">
         <v>19.395652173913046</v>
       </c>
@@ -18338,7 +19228,9 @@
       <c r="AB142" s="8">
         <v>18.112658227848101</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>32.804430000000004</v>
+      </c>
       <c r="AD142" s="8">
         <v>41.598312658227847</v>
       </c>
@@ -18465,7 +19357,9 @@
       <c r="AB143" s="8">
         <v>12.683333333333334</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>17.988461000000001</v>
+      </c>
       <c r="AD143" s="8">
         <v>25.523221348314607</v>
       </c>
@@ -18594,7 +19488,9 @@
       <c r="AB144" s="8">
         <v>3.6731361842105259</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>7.1709589999999999</v>
+      </c>
       <c r="AD144" s="8">
         <v>13.670496894409936</v>
       </c>
@@ -18645,7 +19541,7 @@
         <v>19804</v>
       </c>
       <c r="B145" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C145" s="4">
         <v>44</v>
@@ -18681,25 +19577,61 @@
       <c t="s" r="N145" s="4">
         <v>52</v>
       </c>
-      <c r="O145" s="5"/>
-      <c r="P145" s="5"/>
-      <c r="Q145" s="6"/>
-      <c r="R145" s="7"/>
-      <c r="S145" s="6"/>
-      <c r="T145" s="6"/>
-      <c r="U145" s="6"/>
-      <c r="V145" s="6"/>
-      <c r="W145" s="6"/>
-      <c r="X145" s="8"/>
-      <c r="Y145" s="6"/>
-      <c r="Z145" s="6"/>
-      <c r="AA145" s="8"/>
-      <c r="AB145" s="8"/>
-      <c r="AC145" s="8"/>
-      <c r="AD145" s="8"/>
-      <c r="AE145" s="6"/>
+      <c r="O145" s="5">
+        <v>6550.0699999999997</v>
+      </c>
+      <c r="P145" s="5">
+        <v>6550.0699999999997</v>
+      </c>
+      <c r="Q145" s="6">
+        <v>0.39014767242952764</v>
+      </c>
+      <c r="R145" s="7">
+        <v>80</v>
+      </c>
+      <c r="S145" s="6">
+        <v>0.50943396226415105</v>
+      </c>
+      <c r="T145" s="6">
+        <v>0.35429777086351755</v>
+      </c>
+      <c r="U145" s="6">
+        <v>0.016189933848035212</v>
+      </c>
+      <c r="V145" s="6">
+        <v>0.089665301286856472</v>
+      </c>
+      <c r="W145" s="6">
+        <v>0.045713099249321001</v>
+      </c>
+      <c r="X145" s="8">
+        <v>31.443939393939395</v>
+      </c>
+      <c r="Y145" s="6">
+        <v>0.48484848484848486</v>
+      </c>
+      <c r="Z145" s="6">
+        <v>0.34848484848484851</v>
+      </c>
+      <c r="AA145" s="8">
+        <v>18.241250000000001</v>
+      </c>
+      <c r="AB145" s="8">
+        <v>2.0841463414634145</v>
+      </c>
+      <c r="AC145" s="8">
+        <v>20.663691</v>
+      </c>
+      <c r="AD145" s="8">
+        <v>25.337625757575758</v>
+      </c>
+      <c r="AE145" s="6">
+        <v>0.5757575757575758</v>
+      </c>
       <c r="AF145" s="9"/>
-      <c r="AG145" s="5"/>
+      <c r="AG145" s="5">
+        <v>0</v>
+      </c>
       <c r="AH145" s="10">
         <v>1</v>
       </c>
@@ -18818,7 +19750,9 @@
       <c r="AB146" s="8">
         <v>7.9000000000000004</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>14.14007</v>
+      </c>
       <c r="AD146" s="8">
         <v>20.056027659574468</v>
       </c>
@@ -19080,7 +20014,9 @@
       <c r="AB148" s="8">
         <v>6.5842773584905663</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>16.592490999999999</v>
+      </c>
       <c r="AD148" s="8">
         <v>21.781690140845072</v>
       </c>
@@ -19209,7 +20145,9 @@
       <c r="AB149" s="8">
         <v>8.9638085714285705</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>15.628491</v>
+      </c>
       <c r="AD149" s="8">
         <v>21.617544736842103</v>
       </c>
@@ -19828,7 +20766,9 @@
       <c r="AB154" s="8">
         <v>18.553546808510639</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>49.079396000000003</v>
+      </c>
       <c r="AD154" s="8">
         <v>57.132312244897953</v>
       </c>
@@ -20234,7 +21174,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -20270,25 +21210,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>5461.9799999999996</v>
+      </c>
+      <c r="P158" s="5">
+        <v>5461.9799999999996</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.12569990683915844</v>
+      </c>
+      <c r="R158" s="7">
+        <v>51</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.30136986301369861</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.28869389854961025</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.011688014236595521</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.034574549888501969</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.01010540133797634</v>
+      </c>
+      <c r="X158" s="8">
+        <v>31.626983333333335</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.6088235294117652</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>5.5535714285714288</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>12.630554999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>19.572221428571432</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-243.40000000000001</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -20407,7 +21383,9 @@
       <c r="AB159" s="8">
         <v>4.0174505882352936</v>
       </c>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>9.6719810000000006</v>
+      </c>
       <c r="AD159" s="8">
         <v>16.26896551724138</v>
       </c>
@@ -20532,7 +21510,9 @@
       <c r="AB160" s="8">
         <v>18.009596969696968</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>29.47381</v>
+      </c>
       <c r="AD160" s="8">
         <v>35.777449999999995</v>
       </c>
@@ -20708,7 +21688,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20744,25 +21724,61 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
-      <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="O162" s="5">
+        <v>7543.7399999999998</v>
+      </c>
+      <c r="P162" s="5">
+        <v>7543.7399999999998</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.1148421586204954</v>
+      </c>
+      <c r="R162" s="7">
+        <v>86</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.011494252873563204</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.31871358238751601</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.01616275216272035</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.013382155270462662</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.0013244756579627612</v>
+      </c>
+      <c r="X162" s="8">
+        <v>25.201983333333335</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>7.3329222222222219</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>6.2849585365853651</v>
+      </c>
+      <c r="AC162" s="8">
+        <v>13.79607</v>
+      </c>
+      <c r="AD162" s="8">
+        <v>21.312302380952381</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-1157.3</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20881,7 +21897,9 @@
       <c r="AB163" s="8">
         <v>8.9614814814814814</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>12.107011999999999</v>
+      </c>
       <c r="AD163" s="8">
         <v>19.384987943262413</v>
       </c>
@@ -21158,7 +22176,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -21194,25 +22212,61 @@
       <c t="s" r="N166" s="4">
         <v>52</v>
       </c>
-      <c r="O166" s="5"/>
-      <c r="P166" s="5"/>
-      <c r="Q166" s="6"/>
-      <c r="R166" s="7"/>
-      <c r="S166" s="6"/>
-      <c r="T166" s="6"/>
-      <c r="U166" s="6"/>
-      <c r="V166" s="6"/>
-      <c r="W166" s="6"/>
-      <c r="X166" s="8"/>
-      <c r="Y166" s="6"/>
-      <c r="Z166" s="6"/>
-      <c r="AA166" s="8"/>
-      <c r="AB166" s="8"/>
-      <c r="AC166" s="8"/>
-      <c r="AD166" s="8"/>
-      <c r="AE166" s="6"/>
+      <c r="O166" s="5">
+        <v>10416.530000000001</v>
+      </c>
+      <c r="P166" s="5">
+        <v>10416.530000000001</v>
+      </c>
+      <c r="Q166" s="6">
+        <v>0.078409509729624682</v>
+      </c>
+      <c r="R166" s="7">
+        <v>91</v>
+      </c>
+      <c r="S166" s="6">
+        <v>-0.05208333333333337</v>
+      </c>
+      <c r="T166" s="6">
+        <v>0.24070703007623456</v>
+      </c>
+      <c r="U166" s="6">
+        <v>-0.027844973326050036</v>
+      </c>
+      <c r="V166" s="6">
+        <v>0.042229994057522029</v>
+      </c>
+      <c r="W166" s="6">
+        <v>0.027561001600340994</v>
+      </c>
+      <c r="X166" s="8">
+        <v>42.290643859649123</v>
+      </c>
+      <c r="Y166" s="6">
+        <v>0.08771929824561403</v>
+      </c>
+      <c r="Z166" s="6">
+        <v>0.47368421052631576</v>
+      </c>
+      <c r="AA166" s="8">
+        <v>5.295470652173913</v>
+      </c>
+      <c r="AB166" s="8">
+        <v>23.378363157894739</v>
+      </c>
+      <c r="AC166" s="8">
+        <v>28.278654</v>
+      </c>
+      <c r="AD166" s="8">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="AE166" s="6">
+        <v>0.17543859649122806</v>
+      </c>
       <c r="AF166" s="9"/>
-      <c r="AG166" s="5"/>
+      <c r="AG166" s="5">
+        <v>-50</v>
+      </c>
       <c r="AH166" s="10">
         <v>3</v>
       </c>
@@ -21331,7 +22385,9 @@
       <c r="AB167" s="8">
         <v>32.091818181818184</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>35.445765000000002</v>
+      </c>
       <c r="AD167" s="8">
         <v>40.947767857142857</v>
       </c>
@@ -21460,7 +22516,9 @@
       <c r="AB168" s="8">
         <v>6.2746369565217393</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>11.168963</v>
+      </c>
       <c r="AD168" s="8">
         <v>17.842908510638299</v>
       </c>
@@ -21589,7 +22647,9 @@
       <c r="AB169" s="8">
         <v>5.6826086956521733</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>11.752897000000001</v>
+      </c>
       <c r="AD169" s="8">
         <v>18.698189130434784</v>
       </c>
@@ -21718,7 +22778,9 @@
       <c r="AB170" s="8">
         <v>5.3615934782608692</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>11.87365</v>
+      </c>
       <c r="AD170" s="8">
         <v>18.895289130434783</v>
       </c>
@@ -21847,7 +22909,9 @@
       <c r="AB171" s="8">
         <v>3.9181818181818184</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>8.0306809999999995</v>
+      </c>
       <c r="AD171" s="8">
         <v>14.442130555555556</v>
       </c>
@@ -21976,7 +23040,9 @@
       <c r="AB172" s="8">
         <v>5.5268130434782607</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>8.860144</v>
+      </c>
       <c r="AD172" s="8">
         <v>15.81811739130435</v>
       </c>
@@ -22210,10 +23276,10 @@
         <v>0.024193548387096753</v>
       </c>
       <c r="T174" s="6">
-        <v>0.2783650498750917</v>
+        <v>0.28213882677785312</v>
       </c>
       <c r="U174" s="6">
-        <v>-0.045519283270858177</v>
+        <v>-0.041745506368096749</v>
       </c>
       <c r="V174" s="6">
         <v>0.017493086558555651</v>
@@ -22496,7 +23562,9 @@
       <c r="AB176" s="8">
         <v>19.566160606060606</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>22.678197999999998</v>
+      </c>
       <c r="AD176" s="8">
         <v>29.624748484848485</v>
       </c>
@@ -22625,7 +23693,9 @@
       <c r="AB177" s="8">
         <v>2.4578441176470589</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>6.1810879999999999</v>
+      </c>
       <c r="AD177" s="8">
         <v>12.75138888888889</v>
       </c>
@@ -22754,7 +23824,9 @@
       <c r="AB178" s="8">
         <v>4.0722222222222229</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>8.2318920000000002</v>
+      </c>
       <c r="AD178" s="8">
         <v>15.1786012345679</v>
       </c>
@@ -22881,7 +23953,9 @@
       <c r="AB179" s="8">
         <v>1.1507572727272726</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.9133690000000003</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.856363636363637</v>
       </c>
@@ -22930,7 +24004,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -22966,25 +24040,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>2457.8000000000002</v>
+      </c>
+      <c r="P180" s="5">
+        <v>2457.8000000000002</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>0.21831286123586047</v>
+      </c>
+      <c r="R180" s="7">
+        <v>28</v>
+      </c>
+      <c r="S180" s="6">
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.33855887378956789</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.031159980470339323</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.016980633086500121</v>
+      </c>
+      <c r="X180" s="8">
+        <v>20.707572727272726</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>6.9022999999999994</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>3.0949999999999998</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>10.818611000000001</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>18.18939090909091</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>1</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>-96.299999999999997</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -23025,7 +24135,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23061,25 +24171,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>8010.5299999999997</v>
+      </c>
+      <c r="P181" s="5">
+        <v>8010.5299999999997</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.41340012280416949</v>
+      </c>
+      <c r="R181" s="7">
+        <v>81</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.37288135593220328</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.011464909313116611</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.27012819376495689</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.044180784542346134</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.02814564080029661</v>
+      </c>
+      <c r="X181" s="8">
+        <v>27.194097916666667</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>4.54032962962963</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>10.997807894736843</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>15.394864999999999</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>20.192516326530612</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>0.6875</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23329,7 +24475,9 @@
       <c r="AB183" s="8">
         <v>4.9945454545454542</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>9.6689889999999998</v>
+      </c>
       <c r="AD183" s="8">
         <v>16.995762711864408</v>
       </c>
@@ -23682,7 +24830,9 @@
       <c r="AB186" s="8">
         <v>12.86896551724138</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>25.959769000000001</v>
+      </c>
       <c r="AD186" s="8">
         <v>32.892527586206896</v>
       </c>
@@ -23733,7 +24883,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23769,25 +24919,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>2514</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2514</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.10663520582215147</v>
+      </c>
+      <c r="R187" s="7">
+        <v>32</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32525855210819415</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.17867541766109785</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.12697692919649961</v>
+      </c>
+      <c r="X187" s="8">
+        <v>33.750667999999997</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.52000000000000002</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>9.1473968750000001</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>7.0939999999999994</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>23.388000000000002</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-144.40000000000001</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23830,7 +25016,7 @@
         <v>19928</v>
       </c>
       <c r="B188" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C188" s="4">
         <v>44</v>
@@ -23866,25 +25052,61 @@
       <c t="s" r="N188" s="4">
         <v>52</v>
       </c>
-      <c r="O188" s="5"/>
-      <c r="P188" s="5"/>
-      <c r="Q188" s="6"/>
-      <c r="R188" s="7"/>
-      <c r="S188" s="6"/>
-      <c r="T188" s="6"/>
-      <c r="U188" s="6"/>
-      <c r="V188" s="6"/>
-      <c r="W188" s="6"/>
-      <c r="X188" s="8"/>
-      <c r="Y188" s="6"/>
-      <c r="Z188" s="6"/>
-      <c r="AA188" s="8"/>
-      <c r="AB188" s="8"/>
-      <c r="AC188" s="8"/>
-      <c r="AD188" s="8"/>
-      <c r="AE188" s="6"/>
+      <c r="O188" s="5">
+        <v>6540.9799999999996</v>
+      </c>
+      <c r="P188" s="5">
+        <v>6540.9799999999996</v>
+      </c>
+      <c r="Q188" s="6">
+        <v>0.4208865090312699</v>
+      </c>
+      <c r="R188" s="7">
+        <v>69</v>
+      </c>
+      <c r="S188" s="6">
+        <v>0.078125</v>
+      </c>
+      <c r="T188" s="6">
+        <v>0.18126412250152119</v>
+      </c>
+      <c r="U188" s="6">
+        <v>-0.159619047910252</v>
+      </c>
+      <c r="V188" s="6">
+        <v>0.034478778409351506</v>
+      </c>
+      <c r="W188" s="6">
+        <v>0.012978941993401601</v>
+      </c>
+      <c r="X188" s="8">
+        <v>33.183660784313723</v>
+      </c>
+      <c r="Y188" s="6">
+        <v>0.29411764705882354</v>
+      </c>
+      <c r="Z188" s="6">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="AA188" s="8">
+        <v>4.2519042857142857</v>
+      </c>
+      <c r="AB188" s="8">
+        <v>10.975334</v>
+      </c>
+      <c r="AC188" s="8">
+        <v>15.110588999999999</v>
+      </c>
+      <c r="AD188" s="8">
+        <v>21.862092156862744</v>
+      </c>
+      <c r="AE188" s="6">
+        <v>0.50980392156862742</v>
+      </c>
       <c r="AF188" s="9"/>
-      <c r="AG188" s="5"/>
+      <c r="AG188" s="5">
+        <v>-127.53</v>
+      </c>
       <c r="AH188" s="10">
         <v>4</v>
       </c>
@@ -23925,7 +25147,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23961,25 +25183,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>5989.6700000000001</v>
+      </c>
+      <c r="P189" s="5">
+        <v>5989.6700000000001</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.14486274269942556</v>
+      </c>
+      <c r="R189" s="7">
+        <v>89</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.20270270270270263</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.31112827584825203</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.020987082760819877</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.073953823833366447</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.04701410929149686</v>
+      </c>
+      <c r="X189" s="8">
+        <v>26.206458750000003</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.087499999999999994</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>4.4505494505494507</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>10.990811538461539</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>15.411797999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>21.949791250000001</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.73750000000000004</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24020,7 +25278,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24056,25 +25314,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>12868.709999999999</v>
+      </c>
+      <c r="P190" s="5">
+        <v>12868.709999999999</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>1.3042960538331787</v>
+      </c>
+      <c r="R190" s="7">
+        <v>126</v>
+      </c>
+      <c r="S190" s="6">
+        <v>0.70270270270270263</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.88419550211326547</v>
+      </c>
+      <c r="U190" s="6">
+        <v>0.42567868107992174</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.042627466156281407</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.030721066835758988</v>
+      </c>
+      <c r="X190" s="8">
+        <v>48.096765671641791</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.28358208955223879</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.64179104477611937</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>7.6042968750000002</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>23.597980303030301</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>31.677579999999999</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>38.220646268656715</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.20895522388059701</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-233.58000000000001</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24189,7 +25483,9 @@
       <c r="AB191" s="8">
         <v>10.515217391304347</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>24.371599</v>
+      </c>
       <c r="AD191" s="8">
         <v>31.473189130434779</v>
       </c>
@@ -24445,7 +25741,9 @@
       <c r="AB193" s="8">
         <v>10.794024528301886</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>25.697054999999999</v>
+      </c>
       <c r="AD193" s="8">
         <v>30.875150909090909</v>
       </c>
@@ -24498,7 +25796,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>44</v>
@@ -24534,25 +25832,61 @@
       <c t="s" r="N194" s="4">
         <v>52</v>
       </c>
-      <c r="O194" s="5"/>
-      <c r="P194" s="5"/>
-      <c r="Q194" s="6"/>
-      <c r="R194" s="7"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
-      <c r="X194" s="8"/>
-      <c r="Y194" s="6"/>
-      <c r="Z194" s="6"/>
-      <c r="AA194" s="8"/>
-      <c r="AB194" s="8"/>
-      <c r="AC194" s="8"/>
-      <c r="AD194" s="8"/>
-      <c r="AE194" s="6"/>
+      <c r="O194" s="5">
+        <v>6067.1700000000001</v>
+      </c>
+      <c r="P194" s="5">
+        <v>6067.1700000000001</v>
+      </c>
+      <c r="Q194" s="6">
+        <v>0.41338896343508891</v>
+      </c>
+      <c r="R194" s="7">
+        <v>67</v>
+      </c>
+      <c r="S194" s="6">
+        <v>0.17543859649122817</v>
+      </c>
+      <c r="T194" s="6">
+        <v>0.3268659193660306</v>
+      </c>
+      <c r="U194" s="6">
+        <v>0.0081621414926563787</v>
+      </c>
+      <c r="V194" s="6">
+        <v>0.083869827283560544</v>
+      </c>
+      <c r="W194" s="6">
+        <v>0.051177484725168407</v>
+      </c>
+      <c r="X194" s="8">
+        <v>50.315555555555548</v>
+      </c>
+      <c r="Y194" s="6">
+        <v>0.87234042553191493</v>
+      </c>
+      <c r="Z194" s="6">
+        <v>0.62222222222222223</v>
+      </c>
+      <c r="AA194" s="8">
+        <v>13.267164179104478</v>
+      </c>
+      <c r="AB194" s="8">
+        <v>24.657406666666667</v>
+      </c>
+      <c r="AC194" s="8">
+        <v>38.937548</v>
+      </c>
+      <c r="AD194" s="8">
+        <v>46.274815555555556</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>0.15555555555555556</v>
+      </c>
       <c r="AF194" s="9"/>
-      <c r="AG194" s="5"/>
+      <c r="AG194" s="5">
+        <v>-206.30000000000001</v>
+      </c>
       <c r="AH194" s="10">
         <v>2</v>
       </c>
@@ -24593,7 +25927,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -24629,25 +25963,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>13556.26</v>
+      </c>
+      <c r="P195" s="5">
+        <v>13556.26</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.16099455141216223</v>
+      </c>
+      <c r="R195" s="7">
+        <v>137</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.03007518796992481</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.30314374318580489</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.029548311997556847</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.014669606513890999</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0027083428615267044</v>
+      </c>
+      <c r="X195" s="8">
+        <v>36.155555208333332</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>7.3717174242424237</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>13.218055208333332</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>27.475346875</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.26041666666666669</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-50</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -24766,7 +26134,9 @@
       <c r="AB196" s="8">
         <v>23.997025000000001</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>36.995246000000002</v>
+      </c>
       <c r="AD196" s="8">
         <v>41.243333333333332</v>
       </c>
@@ -25026,7 +26396,9 @@
       <c r="AB198" s="8">
         <v>5.0401222222222222</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>12.775755</v>
+      </c>
       <c r="AD198" s="8">
         <v>19.216665517241381</v>
       </c>
@@ -25208,7 +26580,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25244,25 +26616,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>3129.3499999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>3129.3499999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.18987596863854472</v>
+      </c>
+      <c r="R200" s="7">
+        <v>37</v>
+      </c>
+      <c r="S200" s="6">
+        <v>0.057142857142857162</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.38838097368463104</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.10609551504306006</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.068148337514180257</v>
+      </c>
+      <c r="X200" s="8">
+        <v>31.251332000000001</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.47999999999999998</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>7.5508763157894734</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>6.1459999999999999</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>13.793435000000001</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>20.781332000000003</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.52000000000000002</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-334.69999999999999</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25474,7 +26882,9 @@
       <c r="AB202" s="8">
         <v>8.5210526315789483</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>17.705217999999999</v>
+      </c>
       <c r="AD202" s="8">
         <v>23.911664999999999</v>
       </c>
@@ -25670,10 +27080,10 @@
         <v>-0.28301886792452835</v>
       </c>
       <c r="T204" s="6">
-        <v>0.33059514189145345</v>
+        <v>0.34146517451085645</v>
       </c>
       <c r="U204" s="6">
-        <v>0.023121877414750105</v>
+        <v>0.033991910034153042</v>
       </c>
       <c r="V204" s="6">
         <v>0.017008983607717763</v>
@@ -25696,7 +27106,9 @@
       <c r="AB204" s="8">
         <v>5.4877766666666661</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>12.678888000000001</v>
+      </c>
       <c r="AD204" s="8">
         <v>19.599443333333333</v>
       </c>
@@ -25821,7 +27233,9 @@
       <c r="AB205" s="8">
         <v>5.7819458333333325</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>10.556635</v>
+      </c>
       <c r="AD205" s="8">
         <v>16.94295</v>
       </c>
@@ -25872,7 +27286,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25908,25 +27322,57 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>4237.71</v>
+      </c>
+      <c r="P206" s="5">
+        <v>4237.71</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>52</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
-      <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="T206" s="6">
+        <v>0.34349282985385976</v>
+      </c>
+      <c r="U206" s="6">
+        <v>0.017321383483060428</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.020892415951067913</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.0082747521656743855</v>
+      </c>
+      <c r="X206" s="8">
+        <v>31.075759090909091</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>8.7277770833333328</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>7.5800000000000001</v>
+      </c>
+      <c r="AC206" s="8">
+        <v>16.960303</v>
+      </c>
+      <c r="AD206" s="8">
+        <v>22.878786363636365</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.54545454545454541</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-16.899999999999999</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -25967,7 +27413,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -26003,25 +27449,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>3901.8099999999999</v>
+      </c>
+      <c r="P207" s="5">
+        <v>3901.8099999999999</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>43</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>7.6887393286705402E-06</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.31907755631360829</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.014837344719501974</v>
+      </c>
+      <c r="W207" s="6">
+        <v>-0.019064869893715995</v>
+      </c>
+      <c r="X207" s="8">
+        <v>47.377777777777773</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>17.558129268292682</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>16.568516666666667</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>30.641324999999998</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>37.42592777777778</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.22222222222222221</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-3901.8099999999999</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>
@@ -26136,7 +27614,9 @@
       <c r="AB208" s="8">
         <v>6.4726660000000003</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>14.852731</v>
+      </c>
       <c r="AD208" s="8">
         <v>21.836666000000001</v>
       </c>
@@ -26445,7 +27925,9 @@
       <c r="AB211" s="8">
         <v>12.434235135135136</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>17.218444000000002</v>
+      </c>
       <c r="AD211" s="8">
         <v>23.727192105263157</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-171</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.778.269,04</t>
-  </si>
-  <si>
-    <t>R$ 9.770,71
-R$ 10.002,75</t>
+173</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.793.515,96</t>
+  </si>
+  <si>
+    <t>R$ 9.747,37
+R$ 9.975,24</t>
   </si>
   <si>
     <t>6.1%
 8.4%</t>
   </si>
   <si>
-    <t>102.5</t>
-  </si>
-  <si>
-    <t>(2.3%)</t>
-  </si>
-  <si>
-    <t>(568.6%)</t>
-  </si>
-  <si>
-    <t>(613.3%)</t>
+    <t>102.3</t>
+  </si>
+  <si>
+    <t>(2.0%)</t>
+  </si>
+  <si>
+    <t>(563.5%)</t>
+  </si>
+  <si>
+    <t>(608.0%)</t>
   </si>
   <si>
     <t>2.4%</t>
@@ -950,10 +950,10 @@
     <t>31.6</t>
   </si>
   <si>
-    <t>55.9%</t>
-  </si>
-  <si>
-    <t>20.4%</t>
+    <t>56.1%</t>
+  </si>
+  <si>
+    <t>20.3%</t>
   </si>
   <si>
     <t>7.4</t>
@@ -962,7 +962,7 @@
     <t>8.8</t>
   </si>
   <si>
-    <t>16.4</t>
+    <t>16.5</t>
   </si>
   <si>
     <t>23.0</t>
@@ -971,7 +971,7 @@
     <t>56.8%</t>
   </si>
   <si>
-    <t>-R$ 48.678,43</t>
+    <t>-R$ 48.741,23</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2118,10 +2118,10 @@
         <v>0.32520325203252032</v>
       </c>
       <c r="T6" s="6">
-        <v>0.26026825101793644</v>
+        <v>0.25850843878013335</v>
       </c>
       <c r="U6" s="6">
-        <v>-0.020368419846426598</v>
+        <v>-0.022128232084229725</v>
       </c>
       <c r="V6" s="6">
         <v>0.021672600834328887</v>
@@ -5896,7 +5896,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5932,25 +5932,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>7659.2700000000004</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7659.2700000000004</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.12140267756746637</v>
+      </c>
+      <c r="R36" s="7">
+        <v>99</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.47761194029850751</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.3246439543194064</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.011457449600288279</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.042297177146124895</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.013003262713026176</v>
+      </c>
+      <c r="X36" s="8">
+        <v>34.554872307692307</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.93846153846153846</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.29230769230769232</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>8.0005319148936174</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>9.5220507692307699</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>25.131538461538462</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.41538461538461541</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-62.799999999999997</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6646,7 +6680,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6682,25 +6716,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>7587.6499999999996</v>
+      </c>
+      <c r="P42" s="5">
+        <v>7587.6499999999996</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.11174358974358967</v>
+      </c>
+      <c r="R42" s="7">
+        <v>78</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.16417910447761197</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.30296407978754952</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.012611994491047954</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.02831489328052823</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0029170428261714762</v>
+      </c>
+      <c r="X42" s="8">
+        <v>27.367647058823529</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.61764705882352944</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.488034615384616</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>8.9704545454545439</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>14.543493</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>21.142401470588233</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.67647058823529416</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -26005,7 +26075,9 @@
       <c r="AB195" s="8">
         <v>13.218055208333332</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>20.572742000000002</v>
+      </c>
       <c r="AD195" s="8">
         <v>27.475346875</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
@@ -911,55 +911,58 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-173</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.793.515,96</t>
-  </si>
-  <si>
-    <t>R$ 9.747,37
-R$ 9.975,24</t>
-  </si>
-  <si>
-    <t>6.1%
-8.4%</t>
-  </si>
-  <si>
-    <t>102.3</t>
-  </si>
-  <si>
-    <t>(2.0%)</t>
-  </si>
-  <si>
-    <t>(563.5%)</t>
-  </si>
-  <si>
-    <t>(608.0%)</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>31.6</t>
-  </si>
-  <si>
-    <t>56.1%</t>
-  </si>
-  <si>
-    <t>20.3%</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+175</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 1.815.445,08</t>
+  </si>
+  <si>
+    <t>R$ 9.760,46
+R$ 9.986,55</t>
+  </si>
+  <si>
+    <t>5.9%
+8.1%</t>
+  </si>
+  <si>
+    <t>102.6</t>
+  </si>
+  <si>
+    <t>(2.1%)</t>
+  </si>
+  <si>
+    <t>(556.6%)</t>
+  </si>
+  <si>
+    <t>(601.0%)</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>56.6%</t>
+  </si>
+  <si>
+    <t>20.1%</t>
   </si>
   <si>
     <t>7.4</t>
   </si>
   <si>
-    <t>8.8</t>
+    <t>8.7</t>
   </si>
   <si>
     <t>16.5</t>
@@ -968,7 +971,7 @@
     <t>23.0</t>
   </si>
   <si>
-    <t>56.8%</t>
+    <t>57.1%</t>
   </si>
   <si>
     <t>-R$ 48.741,23</t>
@@ -2249,10 +2252,10 @@
         <v>-0.0098039215686274161</v>
       </c>
       <c r="T7" s="6">
-        <v>0.31212600195375306</v>
+        <v>0.30892558700804584</v>
       </c>
       <c r="U7" s="6">
-        <v>0.013956864196012447</v>
+        <v>0.01075644925030521</v>
       </c>
       <c r="V7" s="6">
         <v>0.033445319612031808</v>
@@ -5666,7 +5669,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5702,25 +5705,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>16195.17</v>
+      </c>
+      <c r="P34" s="5">
+        <v>16195.17</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.16137866967417613</v>
+      </c>
+      <c r="R34" s="7">
+        <v>178</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.091836734693877542</v>
+      </c>
+      <c r="T34" s="6">
+        <v>-0.0030127500977143186</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.32842705572093406</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.045282945470779254</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.0281253608328903</v>
+      </c>
+      <c r="X34" s="8">
+        <v>25.76414892086331</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.91366906474820142</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.093525179856115109</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>13.005179096045199</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.4621556390977446</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>16.002023000000001</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>21.730455395683453</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.76978417266187049</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5974,7 +6013,9 @@
       <c r="AB36" s="8">
         <v>9.5220507692307699</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>18.302354000000001</v>
+      </c>
       <c r="AD36" s="8">
         <v>25.131538461538462</v>
       </c>
@@ -15992,7 +16033,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>29.249442999999999</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19125,7 +19168,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19161,25 +19204,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>5733.9499999999998</v>
+      </c>
+      <c r="P141" s="5">
+        <v>5733.9499999999998</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.093255466324997371</v>
+      </c>
+      <c r="R141" s="7">
+        <v>71</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.18333333333333335</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.25733459482555654</v>
+      </c>
+      <c r="U141" s="6">
+        <v>-0.019073465935349976</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.058798646657190944</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.02034173649927188</v>
+      </c>
+      <c r="X141" s="8">
+        <v>19.804514583333333</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>4.4628014492753616</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>4.4801810810810805</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>8.7819160000000007</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>14.739583333333334</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28411,112 +28490,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-175</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 1.815.445,08</t>
-  </si>
-  <si>
-    <t>R$ 9.760,46
-R$ 9.986,55</t>
-  </si>
-  <si>
-    <t>5.9%
-8.1%</t>
+176</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 1.826.177,34</t>
+  </si>
+  <si>
+    <t>R$ 9.765,65
+R$ 9.990,79</t>
+  </si>
+  <si>
+    <t>5.7%
+7.9%</t>
   </si>
   <si>
     <t>102.6</t>
   </si>
   <si>
-    <t>(2.1%)</t>
-  </si>
-  <si>
-    <t>(556.6%)</t>
-  </si>
-  <si>
-    <t>(601.0%)</t>
+    <t>(2.2%)</t>
+  </si>
+  <si>
+    <t>(552.8%)</t>
+  </si>
+  <si>
+    <t>(597.1%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -950,31 +950,31 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>31.5</t>
-  </si>
-  <si>
-    <t>56.6%</t>
-  </si>
-  <si>
-    <t>20.1%</t>
-  </si>
-  <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>8.7</t>
+    <t>31.6</t>
+  </si>
+  <si>
+    <t>56.4%</t>
+  </si>
+  <si>
+    <t>20.4%</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>8.8</t>
   </si>
   <si>
     <t>16.5</t>
   </si>
   <si>
-    <t>23.0</t>
-  </si>
-  <si>
-    <t>57.1%</t>
-  </si>
-  <si>
-    <t>-R$ 48.741,23</t>
+    <t>23.1</t>
+  </si>
+  <si>
+    <t>56.9%</t>
+  </si>
+  <si>
+    <t>-R$ 48.719,13</t>
   </si>
   <si>
     <t>2.94</t>
@@ -4848,7 +4848,7 @@
         <v>-610.20000000000005</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -11087,7 +11087,7 @@
         <v>-104.7</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -12650,7 +12650,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12684,25 +12684,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>10732.26</v>
+      </c>
+      <c r="P89" s="5">
+        <v>10732.26</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.19498913126639872</v>
+      </c>
+      <c r="R89" s="7">
+        <v>99</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.27737226277372262</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.9096800953387264</v>
+      </c>
+      <c r="U89" s="6">
+        <v>0.59793121858769727</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.013203416614953419</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0017407796680289148</v>
+      </c>
+      <c r="X89" s="8">
+        <v>61.229259999999996</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.91111111111111109</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>11.366666666666665</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>32.437777777777782</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>51.882222222222218</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.022222222222222223</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>22.100000000000001</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14232,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -16563,7 +16597,7 @@
         <v>-35</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -24808,7 +24842,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25775,7 +25809,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27086,7 +27120,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28495,7 +28529,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-04).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-176</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R$ 1.826.177,34</t>
-  </si>
-  <si>
-    <t>R$ 9.765,65
-R$ 9.990,79</t>
+180</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.845.264,84</t>
+  </si>
+  <si>
+    <t>R$ 9.661,07
+R$ 9.874,81</t>
   </si>
   <si>
     <t>5.7%
-7.9%</t>
-  </si>
-  <si>
-    <t>102.6</t>
-  </si>
-  <si>
-    <t>(2.2%)</t>
-  </si>
-  <si>
-    <t>(552.8%)</t>
-  </si>
-  <si>
-    <t>(597.1%)</t>
+7.8%</t>
+  </si>
+  <si>
+    <t>101.5</t>
+  </si>
+  <si>
+    <t>(2.3%)</t>
+  </si>
+  <si>
+    <t>(546.8%)</t>
+  </si>
+  <si>
+    <t>(591.0%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -956,25 +956,25 @@
     <t>56.4%</t>
   </si>
   <si>
-    <t>20.4%</t>
-  </si>
-  <si>
-    <t>7.5</t>
+    <t>20.3%</t>
+  </si>
+  <si>
+    <t>7.4</t>
   </si>
   <si>
     <t>8.8</t>
   </si>
   <si>
-    <t>16.5</t>
-  </si>
-  <si>
-    <t>23.1</t>
-  </si>
-  <si>
-    <t>56.9%</t>
-  </si>
-  <si>
-    <t>-R$ 48.719,13</t>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>23.0</t>
+  </si>
+  <si>
+    <t>57.1%</t>
+  </si>
+  <si>
+    <t>-R$ 48.912,13</t>
   </si>
   <si>
     <t>2.94</t>
@@ -7892,7 +7892,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7928,25 +7928,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1784.7</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1784.7</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.30034681743996261</v>
+      </c>
+      <c r="R51" s="7">
+        <v>19</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0.11764705882352944</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32729310248220989</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.013001344763825851</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.05872499579761304</v>
+      </c>
+      <c r="X51" s="8">
+        <v>55.810412499999998</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>1.7675421052631579</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>58.419450000000005</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>51.9020875</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.375</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8819,7 +8853,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.653999000000001</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20512,7 +20548,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20548,25 +20584,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>6454.1599999999999</v>
+      </c>
+      <c r="P151" s="5">
+        <v>6454.1599999999999</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>0.47079896084955108</v>
+      </c>
+      <c r="R151" s="7">
+        <v>80</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.35593220338983045</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.29513544752531701</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.013631301362222195</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.038244248670624835</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.014148161805719102</v>
+      </c>
+      <c r="X151" s="8">
+        <v>28.333571428571428</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>7.2047912499999995</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.5833333333333335</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>10.884047000000001</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>17.729047142857144</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.6428571428571429</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21262,7 +21334,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21298,25 +21370,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>5588.0799999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>5588.0799999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.15424718878322441</v>
+      </c>
+      <c r="R157" s="7">
+        <v>57</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0.11764705882352944</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.31782379636655167</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.025251034344533366</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.03505756896823238</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.014282991653662796</v>
+      </c>
+      <c r="X157" s="8">
+        <v>29.034751063829788</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.57446808510638303</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.10638297872340426</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>6.7847947368421053</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.8148936170212768</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>10.537588</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>17.486878723404253</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.61702127659574468</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>-100</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -22264,7 +22372,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22300,25 +22408,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>5260.5600000000004</v>
+      </c>
+      <c r="P165" s="5">
+        <v>5260.5600000000004</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.36614489638295222</v>
+      </c>
+      <c r="R165" s="7">
+        <v>51</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.49504950495049505</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.33432801830983772</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.00031125963775719692</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.026014245631643777</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.00038408458415073682</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.832812499999999</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.5724365384615382</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>2.1526031250000002</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>7.3788660000000004</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>14.351040625</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.90625</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-93</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
